--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EC6AB2-75E2-4D0B-8615-C6BD866E1929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3291FB92-A049-4E04-A118-1EAD4E1F1B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>Printing digits in a number</t>
+  </si>
+  <si>
+    <t>Even Odd digit sum and difference</t>
+  </si>
+  <si>
+    <t>Palindrome number</t>
   </si>
 </sst>
 </file>
@@ -412,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
@@ -463,6 +469,16 @@
         <v>8</v>
       </c>
     </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3291FB92-A049-4E04-A118-1EAD4E1F1B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E975A46B-F5E1-46FE-96B0-0348F4BEAEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -67,6 +67,27 @@
   </si>
   <si>
     <t>Palindrome number</t>
+  </si>
+  <si>
+    <t>class array and input elements from user for array
+but using list not array
+and count even elements</t>
+  </si>
+  <si>
+    <t>array creation from importing module array
+searching of element</t>
+  </si>
+  <si>
+    <t>n C++ or Java, you cannot add new data members to an object at runtime. Python can because it stores attributes in a dictionary rather than in a fixed memory layout.</t>
+  </si>
+  <si>
+    <t>1  *  3  *  5  *  7 pattern printing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a  *  c  *  e  *  g </t>
+  </si>
+  <si>
+    <t>ord(char) = ASCII chr(num) = char</t>
   </si>
 </sst>
 </file>
@@ -102,8 +123,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,65 +442,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="150.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E975A46B-F5E1-46FE-96B0-0348F4BEAEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A411BDE-DBCD-422F-A56A-F34820BB3E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t>ord(char) = ASCII chr(num) = char</t>
+  </si>
+  <si>
+    <t>*  *  *  #  #  #  *  *  *  #  #   for 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#  &amp;  #  &amp;
+#  &amp;  #  &amp;
+#  &amp;  #  &amp;
+#  &amp;  #  &amp; </t>
   </si>
 </sst>
 </file>
@@ -442,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
@@ -530,6 +539,16 @@
         <v>16</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A411BDE-DBCD-422F-A56A-F34820BB3E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C480A2-A4F8-4C6D-ADF3-5FBD845DDEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -97,19 +97,172 @@
 #  &amp;  #  &amp;
 #  &amp;  #  &amp;
 #  &amp;  #  &amp; </t>
+  </si>
+  <si>
+    <t>$  $  $  $
+#  #  #  #
+$  $  $  $
+#  #  #  #
+without using if else with char array</t>
+  </si>
+  <si>
+    <t>4  4  4  4
+3  3  3  3
+2  2  2  2
+1  1  1  1  by reversing the outer loop</t>
+  </si>
+  <si>
+    <t>$  @  @  @
+@  $  @  @
+@  @  $  @
+@  @  @  $</t>
+  </si>
+  <si>
+    <t>%  %  %  %  %  %
+%  @  @  @  @  %
+%  @  @  @  @  %
+%  @  @  @  @  %
+%  @  @  @  @  %
+%  %  %  %  %  %</t>
+  </si>
+  <si>
+    <t>%  %  %  %  %  %
+%  %                  %
+%        %            %
+%             %       %
+%                  %  %
+%  %  %  %  %  %</t>
+  </si>
+  <si>
+    <t>* 
+*  *  
+*  *  *  
+*  *  *  *   
+optimized reduced loop printing
+TC &gt;O(N^2/2)</t>
+  </si>
+  <si>
+    <t>*
+*  *
+*  $  *
+*  $  $  *
+*  $  $  $  *
+*  *  *  *  *  *</t>
+  </si>
+  <si>
+    <t>*
+*  *
+*      *
+*          *
+*              *
+*  *  *  *  *  *</t>
+  </si>
+  <si>
+    <t>String input and length of string</t>
+  </si>
+  <si>
+    <t>Count capitle and small leters in string</t>
+  </si>
+  <si>
+    <t>toggle the letters in spring</t>
+  </si>
+  <si>
+    <t>o
+lo
+llo
+ello
+Hello</t>
+  </si>
+  <si>
+    <t>printing number in octal hexadecimal and binary</t>
+  </si>
+  <si>
+    <t>checking bit on position on or of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decimal to Binary using while loop like digit but % 2 and / 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle the 7th and 12th bit of number </t>
+  </si>
+  <si>
+    <t>Toggle the bit at ith position</t>
+  </si>
+  <si>
+    <t>Accept number from user and 
+off the bit at 23th position if its on</t>
+  </si>
+  <si>
+    <t>Count the number of ON and OFF bits in a number.</t>
+  </si>
+  <si>
+    <t>Brian Kernighan's Algorithm for finding the ON bits in the number
+best approach</t>
+  </si>
+  <si>
+    <t>Multiplying and dividing by 2 using right and left shift operator</t>
+  </si>
+  <si>
+    <t>Even Odd using bitwise
+as if LSB is off its even 
+as no extra 1 is added</t>
+  </si>
+  <si>
+    <t>accept number from user and 
+check if it is power of 2 or not 
+using bitwise operations</t>
+  </si>
+  <si>
+    <t>return the position of leftmost and rightmost on bit</t>
+  </si>
+  <si>
+    <t>Reverse all bits of number</t>
+  </si>
+  <si>
+    <t>swap two numbers with xor operation</t>
+  </si>
+  <si>
+    <t>Check whether two numbers are equal using XOR</t>
+  </si>
+  <si>
+    <t>find unique element from array if other element appears twice in array</t>
+  </si>
+  <si>
+    <t>find missing number from 1 to N</t>
+  </si>
+  <si>
+    <t>Set the last N bits.</t>
+  </si>
+  <si>
+    <t>Singly Linear Linked List
+Insert and Display</t>
+  </si>
+  <si>
+    <t>Singly Linear Linked List
+All functions</t>
+  </si>
+  <si>
+    <t>Singly Circular Linked List
+All functions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9AA83A"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -132,10 +285,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,10 +607,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="150.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -549,6 +705,171 @@
         <v>18</v>
       </c>
     </row>
+    <row r="18" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C480A2-A4F8-4C6D-ADF3-5FBD845DDEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4921E7-25F7-4909-BF47-13E7FE4F6D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -243,6 +243,10 @@
   </si>
   <si>
     <t>Singly Circular Linked List
+All functions</t>
+  </si>
+  <si>
+    <t>Doubly Linear Linked List
 All functions</t>
   </si>
 </sst>
@@ -607,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.5703125" bestFit="1" customWidth="1"/>
@@ -870,6 +874,11 @@
         <v>51</v>
       </c>
     </row>
+    <row r="51" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4921E7-25F7-4909-BF47-13E7FE4F6D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE7FCF6-D4AE-4156-90B4-9ED8C564817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -248,6 +248,40 @@
   <si>
     <t>Doubly Linear Linked List
 All functions</t>
+  </si>
+  <si>
+    <t>Doubly Circular Linked List
+All functions</t>
+  </si>
+  <si>
+    <t>Factorial of Number with recursion</t>
+  </si>
+  <si>
+    <t>digit display and sum of all digits of a number 
+tail Recursive apporch</t>
+  </si>
+  <si>
+    <t>digit display and sum of all digits of a number 
+head Recursive apporch</t>
+  </si>
+  <si>
+    <t>Check Palindrome using Recursion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addition of N numbers </t>
+  </si>
+  <si>
+    <t>Addition of N numbers 
+with elements from user</t>
+  </si>
+  <si>
+    <t>Stack code</t>
+  </si>
+  <si>
+    <t>Queue Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queue code with Display Recursive not good </t>
   </si>
 </sst>
 </file>
@@ -289,13 +323,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,10 +648,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="87.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="150.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -879,6 +916,56 @@
         <v>52</v>
       </c>
     </row>
+    <row r="52" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Python code statements.xlsx
+++ b/Python code statements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHREYA\Desktop\Python Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE7FCF6-D4AE-4156-90B4-9ED8C564817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C556260-E6F9-430D-A283-F98B31E74DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{004C20B9-D5AA-4773-B689-5502DB922027}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>print Jay Ganesh</t>
   </si>
@@ -282,6 +282,33 @@
   </si>
   <si>
     <t xml:space="preserve">Queue code with Display Recursive not good </t>
+  </si>
+  <si>
+    <t>Queue reverse Display
+Minimum and Maximum element</t>
+  </si>
+  <si>
+    <t>factirial with recursion 
+highorder operator for returning list of squares of numbers
+from given list</t>
+  </si>
+  <si>
+    <t>Even odd lambda function with 2 approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filter and lambda function for getting numbers greater than 50
+map function to take input list from user </t>
+  </si>
+  <si>
+    <t xml:space="preserve">inner function and outer function </t>
+  </si>
+  <si>
+    <t>MultiThreading in python
+using functions and without join</t>
+  </si>
+  <si>
+    <t>MultiThreading in python
+using functions and with join</t>
   </si>
 </sst>
 </file>
@@ -648,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B0B21-D0B4-41AD-AEDB-F9C0466522F6}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="87.42578125" bestFit="1" customWidth="1"/>
@@ -966,6 +993,41 @@
         <v>62</v>
       </c>
     </row>
+    <row r="62" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
